--- a/sat-math.xlsx
+++ b/sat-math.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/019252dbb137ead9/Desktop/sat-math-platform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B4C277B-D693-4B8D-9C1B-6ABEAF22BB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{3B4C277B-D693-4B8D-9C1B-6ABEAF22BB21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F942CD2A-7D0A-4ADE-A6DA-8DED70DF8C32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{799D0C06-C02C-4E1A-902A-9291D8E60AD8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Chapter</t>
   </si>
@@ -52,6 +52,21 @@
   </si>
   <si>
     <t>https://docs.google.com/presentation/d/1FOxWjRonUR7_wAVP7rY6neo9uOTvA7tw/edit?usp=sharing&amp;ouid=117376786256425211529&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>03 - Ratio, Proportion &amp; Rates</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1uza-1j-mCyO_IXDj4xAJIIVzEhJfiG9uPUVdPQYy1N0/edit?usp=sharing</t>
+  </si>
+  <si>
+    <t>04 - Percentages</t>
+  </si>
+  <si>
+    <t>https://docs.google.com/presentation/d/1JT0Qi9iRYKW-q7P2XPWq3iupZA-vU_vU/edit?usp=sharing&amp;ouid=117376786256425211529&amp;rtpof=true&amp;sd=true</t>
+  </si>
+  <si>
+    <t>05 - Linear Equations</t>
   </si>
 </sst>
 </file>
@@ -414,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F5F6B6B-1D20-4A9A-9F0A-DC61BF76A795}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.109375" customWidth="1"/>
@@ -445,10 +460,33 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{EE83691E-66F6-47E4-A050-29B525281C21}"/>
     <hyperlink ref="B3" r:id="rId2" xr:uid="{24F293CC-E446-4971-8DF3-CAF225DE5561}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{3E8EBCD7-EF30-4752-AB77-339A44A7C00E}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{CB2FBAF4-754D-4198-ACB6-ADFD68DD6368}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
